--- a/cucumber-for-appian/src/test/resources/testdata/End2End/08_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/08_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="163">
   <si>
     <t>TC ID</t>
   </si>
@@ -411,6 +411,111 @@
   </si>
   <si>
     <t>8</t>
+  </si>
+  <si>
+    <t>S992CYU</t>
+  </si>
+  <si>
+    <t>VOLVO EX30</t>
+  </si>
+  <si>
+    <t>18 Jun 2026</t>
+  </si>
+  <si>
+    <t>13012</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>McInnes</t>
+  </si>
+  <si>
+    <t>01/05/1987</t>
+  </si>
+  <si>
+    <t>369875622</t>
+  </si>
+  <si>
+    <t>andrew.mcinnes@raytheon.com.au.test</t>
+  </si>
+  <si>
+    <t>Raytheon Australia Pty Ltd</t>
+  </si>
+  <si>
+    <t>26 May 2026</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>EZW18T</t>
+  </si>
+  <si>
+    <t>TESLA MODEL Y</t>
+  </si>
+  <si>
+    <t>21 Jun 2026</t>
+  </si>
+  <si>
+    <t>29379</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Lau</t>
+  </si>
+  <si>
+    <t>30/04/1977</t>
+  </si>
+  <si>
+    <t>369852147</t>
+  </si>
+  <si>
+    <t>jack.lau@optus.com.au.test</t>
+  </si>
+  <si>
+    <t>Optus Administration Pty Ltd</t>
+  </si>
+  <si>
+    <t>23 Mar 2026</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>FPJ50N</t>
+  </si>
+  <si>
+    <t>BYD DOLPHIN</t>
+  </si>
+  <si>
+    <t>1 Jul 2026</t>
+  </si>
+  <si>
+    <t>8957</t>
+  </si>
+  <si>
+    <t>Sudeep</t>
+  </si>
+  <si>
+    <t>Shakya</t>
+  </si>
+  <si>
+    <t>27 Jun 1986</t>
+  </si>
+  <si>
+    <t>333665987</t>
+  </si>
+  <si>
+    <t>sudeep.shakya@outlook.com.test</t>
+  </si>
+  <si>
+    <t>QBE Management Services Pty Ltd</t>
+  </si>
+  <si>
+    <t>30 Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -1602,15 +1707,15 @@
         <v>46</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>24802.0</v>
+        <v>8958.0</v>
       </c>
       <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>24802.0</v>
+        <v>8958.0</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1647,14 +1752,14 @@
       </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>51</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>24,802 km</v>
+        <v>8,958 km</v>
       </c>
       <c r="W2" s="7" t="s">
         <v>52</v>
@@ -1673,57 +1778,57 @@
         <v>55</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>Stephen Jackson</v>
+        <v>Sudeep Shakya</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="AI2" s="7" t="s">
         <v>61</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v>MG MG ZS - 1XZ2BI</v>
+        <v>BYD DOLPHIN - FPJ50N</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="AN2" s="7" t="s">
         <v>65</v>
       </c>
       <c r="AO2" s="7"/>
       <c r="AP2" s="7" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="AQ2" s="7" t="str">
         <f>TEXT(C2,"#,##0")</f>
-        <v>24,801</v>
+        <v>8,957</v>
       </c>
       <c r="AR2" s="7" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="AS2" s="7" t="str">
         <f>"Intend to Terminate on "&amp;TEXT(T2,"dd mmmm yyyy")</f>
-        <v>Intend to Terminate on 19 February 2026</v>
+        <v>Intend to Terminate on 30 July 2026</v>
       </c>
       <c r="AT2" s="8"/>
     </row>
